--- a/output/pdf_financials_xlsx/SN.H.xlsx
+++ b/output/pdf_financials_xlsx/SN.H.xlsx
@@ -7059,25 +7059,25 @@
         <v>1.844284</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.844284</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.844284</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.16008</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.541637</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.663511</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.663511</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.663511</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -10496,7 +10496,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -11108,7 +11112,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11817,7 +11825,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -12514,7 +12526,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SN.H.xlsx
+++ b/output/pdf_financials_xlsx/SN.H.xlsx
@@ -1141,31 +1141,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.297693</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.471498</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.25037</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.125637</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.07209</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.028389</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00895</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001082</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001673</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2255,31 +2255,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.413725</v>
+        <v>-2.711418</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.839625</v>
+        <v>1.368127</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.519074</v>
+        <v>-1.769444</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.192606</v>
+        <v>-2.318243</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.120783</v>
+        <v>-1.192873</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.114756</v>
+        <v>-1.143145</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.045446</v>
+        <v>-6.054396</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.801082</v>
+        <v>-1.802164</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.458564</v>
+        <v>-0.460237</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.857149</v>
@@ -2399,31 +2399,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.413725</v>
+        <v>-2.711418</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.839625</v>
+        <v>1.368127</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.519074</v>
+        <v>-1.769444</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.192606</v>
+        <v>-2.318243</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.120783</v>
+        <v>-1.192873</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.114756</v>
+        <v>-1.143145</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.045446</v>
+        <v>-6.054396</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.801082</v>
+        <v>-1.802164</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.458564</v>
+        <v>-0.460237</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.857149</v>
@@ -28604,7 +28604,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -31045,7 +31045,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E222" s="5" t="n">
